--- a/backend/data/financials_by_company/0QW.F.xlsx
+++ b/backend/data/financials_by_company/0QW.F.xlsx
@@ -667,564 +667,564 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
+        <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>-3396461.481359</v>
+        <v>-540034.0122070001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.195233</v>
+        <v>0.09057900000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>247619000</v>
+        <v>-2220000</v>
       </c>
       <c r="E2" t="n">
-        <v>-17397000</v>
+        <v>-5962000</v>
       </c>
       <c r="F2" t="n">
-        <v>-17397000</v>
+        <v>-5962000</v>
       </c>
       <c r="G2" t="n">
-        <v>48785000</v>
+        <v>-177006000</v>
       </c>
       <c r="H2" t="n">
-        <v>102382000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>120920000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>844574000</v>
+      </c>
       <c r="J2" t="n">
-        <v>230222000</v>
+        <v>-8182000</v>
       </c>
       <c r="K2" t="n">
-        <v>127840000</v>
+        <v>-129102000</v>
       </c>
       <c r="L2" t="n">
-        <v>-65627000</v>
+        <v>-79375000</v>
       </c>
       <c r="M2" t="n">
-        <v>67220000</v>
+        <v>65534000</v>
       </c>
       <c r="N2" t="n">
-        <v>2032000</v>
+        <v>595000</v>
       </c>
       <c r="O2" t="n">
-        <v>62785538.518641</v>
+        <v>-171584034.012207</v>
       </c>
       <c r="P2" t="n">
-        <v>48785000</v>
+        <v>-177006000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1891856000</v>
+        <v>881854000</v>
       </c>
       <c r="R2" t="n">
-        <v>17498000</v>
+        <v>3585000</v>
       </c>
       <c r="S2" t="n">
-        <v>142585000</v>
+        <v>-109299000</v>
       </c>
       <c r="T2" t="n">
-        <v>125029312</v>
+        <v>124668915</v>
       </c>
       <c r="U2" t="n">
-        <v>120335698</v>
+        <v>122827248</v>
       </c>
       <c r="V2" t="n">
-        <v>0.39</v>
+        <v>-1.474</v>
       </c>
       <c r="W2" t="n">
-        <v>0.405</v>
+        <v>-1.474</v>
       </c>
       <c r="X2" t="n">
-        <v>48785000</v>
+        <v>-177006000</v>
       </c>
       <c r="Y2" t="n">
-        <v>48785000</v>
+        <v>-177006000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>48785000</v>
+        <v>-177006000</v>
       </c>
       <c r="AB2" t="n">
-        <v>48785000</v>
+        <v>-177006000</v>
       </c>
       <c r="AC2" t="n">
-        <v>48785000</v>
+        <v>-177006000</v>
       </c>
       <c r="AD2" t="n">
-        <v>11835000</v>
+        <v>-17630000</v>
       </c>
       <c r="AE2" t="n">
-        <v>60620000</v>
+        <v>-194636000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-17397000</v>
+        <v>-5962000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1701000</v>
+        <v>1830000</v>
       </c>
       <c r="AH2" t="n">
-        <v>19098000</v>
+        <v>4132000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-65627000</v>
+        <v>-79375000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>439000</v>
+        <v>14436000</v>
       </c>
       <c r="AK2" t="n">
-        <v>67220000</v>
+        <v>65534000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2032000</v>
+        <v>595000</v>
       </c>
       <c r="AM2" t="n">
-        <v>143644000</v>
+        <v>-109299000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1891856000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1896009000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-4139000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-4139000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>37280000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>37280000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>37280000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-72019000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>844574000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>2035500000</v>
+        <v>772555000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2035500000</v>
+        <v>772555000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
-        <v>17127080.642132</v>
+        <v>7856559.062012</v>
       </c>
       <c r="C3" t="n">
-        <v>0.34166</v>
+        <v>0.26655</v>
       </c>
       <c r="D3" t="n">
-        <v>216962000</v>
+        <v>170497000</v>
       </c>
       <c r="E3" t="n">
-        <v>50129000</v>
+        <v>29475000</v>
       </c>
       <c r="F3" t="n">
-        <v>50129000</v>
+        <v>29475000</v>
       </c>
       <c r="G3" t="n">
-        <v>59587000</v>
+        <v>19267000</v>
       </c>
       <c r="H3" t="n">
-        <v>109741000</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>116845000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1640202000</v>
+      </c>
       <c r="J3" t="n">
-        <v>267091000</v>
+        <v>199972000</v>
       </c>
       <c r="K3" t="n">
-        <v>157350000</v>
+        <v>83127000</v>
       </c>
       <c r="L3" t="n">
-        <v>-66734000</v>
+        <v>-58310000</v>
       </c>
       <c r="M3" t="n">
-        <v>66839000</v>
+        <v>56858000</v>
       </c>
       <c r="N3" t="n">
-        <v>1351000</v>
+        <v>531000</v>
       </c>
       <c r="O3" t="n">
-        <v>26585080.642132</v>
+        <v>-2351440.937988</v>
       </c>
       <c r="P3" t="n">
-        <v>59587000</v>
+        <v>19267000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1817928000</v>
+        <v>1685373000</v>
       </c>
       <c r="R3" t="n">
-        <v>17484000</v>
+        <v>8809000</v>
       </c>
       <c r="S3" t="n">
-        <v>106040000</v>
+        <v>55104000</v>
       </c>
       <c r="T3" t="n">
-        <v>128264108</v>
+        <v>126825345</v>
       </c>
       <c r="U3" t="n">
-        <v>125453877</v>
+        <v>126825345</v>
       </c>
       <c r="V3" t="n">
-        <v>0.465</v>
+        <v>0.152</v>
       </c>
       <c r="W3" t="n">
-        <v>0.475</v>
+        <v>0.152</v>
       </c>
       <c r="X3" t="n">
-        <v>59587000</v>
+        <v>19267000</v>
       </c>
       <c r="Y3" t="n">
-        <v>59587000</v>
+        <v>19267000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>59587000</v>
+        <v>19267000</v>
       </c>
       <c r="AB3" t="n">
-        <v>59587000</v>
+        <v>19267000</v>
       </c>
       <c r="AC3" t="n">
-        <v>59587000</v>
+        <v>19267000</v>
       </c>
       <c r="AD3" t="n">
-        <v>30924000</v>
+        <v>7002000</v>
       </c>
       <c r="AE3" t="n">
-        <v>90511000</v>
+        <v>26269000</v>
       </c>
       <c r="AF3" t="n">
-        <v>50129000</v>
+        <v>-22384000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-88416000</v>
+        <v>-2046000</v>
       </c>
       <c r="AH3" t="n">
-        <v>38287000</v>
+        <v>24430000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-66734000</v>
+        <v>-58310000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1246000</v>
+        <v>1983000</v>
       </c>
       <c r="AK3" t="n">
-        <v>66839000</v>
+        <v>56858000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1351000</v>
+        <v>531000</v>
       </c>
       <c r="AM3" t="n">
-        <v>107116000</v>
+        <v>55104000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1817928000</v>
+        <v>1685373000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1817982000</v>
+        <v>1714757000</v>
       </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>45171000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>45171000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>100275000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1640202000</v>
+      </c>
       <c r="AV3" t="n">
-        <v>1925044000</v>
+        <v>1740477000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1925044000</v>
+        <v>1740477000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
-        <v>7856559.062012</v>
+        <v>17127080.642132</v>
       </c>
       <c r="C4" t="n">
-        <v>0.26655</v>
+        <v>0.34166</v>
       </c>
       <c r="D4" t="n">
-        <v>170497000</v>
+        <v>216962000</v>
       </c>
       <c r="E4" t="n">
-        <v>29475000</v>
+        <v>50129000</v>
       </c>
       <c r="F4" t="n">
-        <v>29475000</v>
+        <v>50129000</v>
       </c>
       <c r="G4" t="n">
-        <v>19267000</v>
+        <v>59587000</v>
       </c>
       <c r="H4" t="n">
-        <v>116845000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1640202000</v>
-      </c>
+        <v>109741000</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>199972000</v>
+        <v>267091000</v>
       </c>
       <c r="K4" t="n">
-        <v>83127000</v>
+        <v>157350000</v>
       </c>
       <c r="L4" t="n">
-        <v>-58310000</v>
+        <v>-66734000</v>
       </c>
       <c r="M4" t="n">
-        <v>56858000</v>
+        <v>66839000</v>
       </c>
       <c r="N4" t="n">
-        <v>531000</v>
+        <v>1351000</v>
       </c>
       <c r="O4" t="n">
-        <v>-2351440.937988</v>
+        <v>26585080.642132</v>
       </c>
       <c r="P4" t="n">
-        <v>19267000</v>
+        <v>59587000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1685373000</v>
+        <v>1817928000</v>
       </c>
       <c r="R4" t="n">
-        <v>8809000</v>
+        <v>17484000</v>
       </c>
       <c r="S4" t="n">
-        <v>55104000</v>
+        <v>106040000</v>
       </c>
       <c r="T4" t="n">
-        <v>126825345</v>
+        <v>128264108</v>
       </c>
       <c r="U4" t="n">
-        <v>126825345</v>
+        <v>125453877</v>
       </c>
       <c r="V4" t="n">
-        <v>0.152</v>
+        <v>0.465</v>
       </c>
       <c r="W4" t="n">
-        <v>0.152</v>
+        <v>0.475</v>
       </c>
       <c r="X4" t="n">
-        <v>19267000</v>
+        <v>59587000</v>
       </c>
       <c r="Y4" t="n">
-        <v>19267000</v>
+        <v>59587000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>19267000</v>
+        <v>59587000</v>
       </c>
       <c r="AB4" t="n">
-        <v>19267000</v>
+        <v>59587000</v>
       </c>
       <c r="AC4" t="n">
-        <v>19267000</v>
+        <v>59587000</v>
       </c>
       <c r="AD4" t="n">
-        <v>7002000</v>
+        <v>30924000</v>
       </c>
       <c r="AE4" t="n">
-        <v>26269000</v>
+        <v>90511000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-22384000</v>
+        <v>50129000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2046000</v>
+        <v>-88416000</v>
       </c>
       <c r="AH4" t="n">
-        <v>24430000</v>
+        <v>38287000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-58310000</v>
+        <v>-66734000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1983000</v>
+        <v>1246000</v>
       </c>
       <c r="AK4" t="n">
-        <v>56858000</v>
+        <v>66839000</v>
       </c>
       <c r="AL4" t="n">
-        <v>531000</v>
+        <v>1351000</v>
       </c>
       <c r="AM4" t="n">
-        <v>55104000</v>
+        <v>107116000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1685373000</v>
+        <v>1817928000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1714757000</v>
+        <v>1817982000</v>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>45171000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>45171000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>100275000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1640202000</v>
-      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>1740477000</v>
+        <v>1925044000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1740477000</v>
+        <v>1925044000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
+        <v>45504</v>
       </c>
       <c r="B5" t="n">
-        <v>-540034.0122070001</v>
+        <v>-3396461.481359</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09057900000000001</v>
+        <v>0.195233</v>
       </c>
       <c r="D5" t="n">
-        <v>-2220000</v>
+        <v>247619000</v>
       </c>
       <c r="E5" t="n">
-        <v>-5962000</v>
+        <v>-17397000</v>
       </c>
       <c r="F5" t="n">
-        <v>-5962000</v>
+        <v>-17397000</v>
       </c>
       <c r="G5" t="n">
-        <v>-177006000</v>
+        <v>48785000</v>
       </c>
       <c r="H5" t="n">
-        <v>120920000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>844574000</v>
-      </c>
+        <v>102382000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>-8182000</v>
+        <v>230222000</v>
       </c>
       <c r="K5" t="n">
-        <v>-129102000</v>
+        <v>127840000</v>
       </c>
       <c r="L5" t="n">
-        <v>-79375000</v>
+        <v>-65627000</v>
       </c>
       <c r="M5" t="n">
-        <v>65534000</v>
+        <v>67220000</v>
       </c>
       <c r="N5" t="n">
-        <v>595000</v>
+        <v>2032000</v>
       </c>
       <c r="O5" t="n">
-        <v>-171584034.012207</v>
+        <v>62785538.518641</v>
       </c>
       <c r="P5" t="n">
-        <v>-177006000</v>
+        <v>48785000</v>
       </c>
       <c r="Q5" t="n">
-        <v>881854000</v>
+        <v>1891856000</v>
       </c>
       <c r="R5" t="n">
-        <v>3585000</v>
+        <v>17498000</v>
       </c>
       <c r="S5" t="n">
-        <v>-109299000</v>
+        <v>142585000</v>
       </c>
       <c r="T5" t="n">
-        <v>124668915</v>
+        <v>125029312</v>
       </c>
       <c r="U5" t="n">
-        <v>122827248</v>
+        <v>120335698</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.474</v>
+        <v>0.39</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.474</v>
+        <v>0.405</v>
       </c>
       <c r="X5" t="n">
-        <v>-177006000</v>
+        <v>48785000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-177006000</v>
+        <v>48785000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-177006000</v>
+        <v>48785000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-177006000</v>
+        <v>48785000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-177006000</v>
+        <v>48785000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-17630000</v>
+        <v>11835000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-194636000</v>
+        <v>60620000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-5962000</v>
+        <v>-17397000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1830000</v>
+        <v>-1701000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4132000</v>
+        <v>19098000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-79375000</v>
+        <v>-65627000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14436000</v>
+        <v>439000</v>
       </c>
       <c r="AK5" t="n">
-        <v>65534000</v>
+        <v>67220000</v>
       </c>
       <c r="AL5" t="n">
-        <v>595000</v>
+        <v>2032000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-109299000</v>
+        <v>143644000</v>
       </c>
       <c r="AN5" t="n">
-        <v>37280000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>37280000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>37280000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-72019000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>844574000</v>
-      </c>
+        <v>1891856000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1896009000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-4139000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-4139000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>772555000</v>
+        <v>2035500000</v>
       </c>
       <c r="AW5" t="n">
-        <v>772555000</v>
+        <v>2035500000</v>
       </c>
     </row>
   </sheetData>
@@ -1530,231 +1530,229 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
-      </c>
-      <c r="B2" t="n">
-        <v>7637465</v>
-      </c>
+        <v>44408</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>115984731</v>
+        <v>128750155</v>
       </c>
       <c r="D2" t="n">
-        <v>123622196</v>
+        <v>128750155</v>
       </c>
       <c r="E2" t="n">
-        <v>661901000</v>
+        <v>829231000</v>
       </c>
       <c r="F2" t="n">
-        <v>1137376000</v>
+        <v>1414697000</v>
       </c>
       <c r="G2" t="n">
-        <v>395694000</v>
+        <v>272619000</v>
       </c>
       <c r="H2" t="n">
-        <v>1120761000</v>
+        <v>1152616000</v>
       </c>
       <c r="I2" t="n">
-        <v>-229251000</v>
+        <v>-244111000</v>
       </c>
       <c r="J2" t="n">
-        <v>395694000</v>
+        <v>272619000</v>
       </c>
       <c r="K2" t="n">
-        <v>418242000</v>
+        <v>540058000</v>
       </c>
       <c r="L2" t="n">
-        <v>401627000</v>
+        <v>277977000</v>
       </c>
       <c r="M2" t="n">
-        <v>1120761000</v>
+        <v>1152616000</v>
       </c>
       <c r="N2" t="n">
-        <v>401627000</v>
+        <v>277977000</v>
       </c>
       <c r="O2" t="n">
-        <v>401627000</v>
+        <v>277977000</v>
       </c>
       <c r="P2" t="n">
-        <v>44571000</v>
+        <v>-87207000</v>
       </c>
       <c r="Q2" t="n">
-        <v>145610000</v>
+        <v>145631000</v>
       </c>
       <c r="R2" t="n">
-        <v>2472000</v>
+        <v>2575000</v>
       </c>
       <c r="S2" t="n">
-        <v>2472000</v>
+        <v>2575000</v>
       </c>
       <c r="T2" t="n">
-        <v>1502743000</v>
+        <v>1731681000</v>
       </c>
       <c r="U2" t="n">
-        <v>1151354000</v>
+        <v>1396057000</v>
       </c>
       <c r="V2" t="n">
-        <v>4073000</v>
+        <v>37643000</v>
       </c>
       <c r="W2" t="n">
-        <v>59487000</v>
+        <v>16546000</v>
       </c>
       <c r="X2" t="n">
-        <v>1087794000</v>
+        <v>1341868000</v>
       </c>
       <c r="Y2" t="n">
-        <v>368660000</v>
+        <v>467229000</v>
       </c>
       <c r="Z2" t="n">
-        <v>719134000</v>
+        <v>874639000</v>
       </c>
       <c r="AA2" t="n">
-        <v>351389000</v>
+        <v>335624000</v>
       </c>
       <c r="AB2" t="n">
-        <v>49582000</v>
+        <v>72829000</v>
       </c>
       <c r="AC2" t="n">
-        <v>49582000</v>
+        <v>72829000</v>
       </c>
       <c r="AD2" t="n">
-        <v>3047000</v>
+        <v>3004000</v>
       </c>
       <c r="AE2" t="n">
-        <v>219998000</v>
+        <v>183914000</v>
       </c>
       <c r="AF2" t="n">
-        <v>16019000</v>
+        <v>27759000</v>
       </c>
       <c r="AG2" t="n">
-        <v>66698000</v>
+        <v>44237000</v>
       </c>
       <c r="AH2" t="n">
-        <v>137281000</v>
+        <v>111918000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1904370000</v>
+        <v>2009658000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1782232000</v>
+        <v>1918145000</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>18290000</v>
+        <v>10533000</v>
       </c>
       <c r="AM2" t="n">
-        <v>5933000</v>
+        <v>5358000</v>
       </c>
       <c r="AN2" t="n">
-        <v>5933000</v>
+        <v>5358000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1756815000</v>
+        <v>1902254000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1264336000</v>
+        <v>-1146188000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3021151000</v>
+        <v>3048442000</v>
       </c>
       <c r="AR2" t="n">
-        <v>57555000</v>
+        <v>63868000</v>
       </c>
       <c r="AS2" t="n">
-        <v>373338000</v>
+        <v>558897000</v>
       </c>
       <c r="AT2" t="n">
-        <v>815134000</v>
+        <v>700311000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1775124000</v>
+        <v>1725366000</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>122138000</v>
+        <v>91513000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1358000</v>
+        <v>1638000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2488000</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17730000</v>
+        <v>12924000</v>
       </c>
       <c r="BA2" t="n">
-        <v>28404000</v>
+        <v>26853000</v>
       </c>
       <c r="BB2" t="n">
-        <v>28404000</v>
+        <v>26853000</v>
       </c>
       <c r="BC2" t="n">
-        <v>8846000</v>
+        <v>3503000</v>
       </c>
       <c r="BD2" t="n">
-        <v>6079000</v>
+        <v>1187000</v>
       </c>
       <c r="BE2" t="n">
-        <v>57233000</v>
+        <v>45408000</v>
       </c>
       <c r="BF2" t="n">
-        <v>57233000</v>
+        <v>45408000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
-        <v>6360365</v>
+        <v>4416005</v>
       </c>
       <c r="C3" t="n">
-        <v>122389790</v>
+        <v>124334150</v>
       </c>
       <c r="D3" t="n">
         <v>128750155</v>
       </c>
       <c r="E3" t="n">
-        <v>640470000</v>
+        <v>886083000</v>
       </c>
       <c r="F3" t="n">
-        <v>1175123000</v>
+        <v>1405595000</v>
       </c>
       <c r="G3" t="n">
-        <v>406553000</v>
+        <v>316476000</v>
       </c>
       <c r="H3" t="n">
-        <v>1140701000</v>
+        <v>1248315000</v>
       </c>
       <c r="I3" t="n">
-        <v>-228147000</v>
+        <v>-237800000</v>
       </c>
       <c r="J3" t="n">
-        <v>406553000</v>
+        <v>316476000</v>
       </c>
       <c r="K3" t="n">
-        <v>447480000</v>
+        <v>479165000</v>
       </c>
       <c r="L3" t="n">
-        <v>413058000</v>
+        <v>321885000</v>
       </c>
       <c r="M3" t="n">
-        <v>1140701000</v>
+        <v>1248315000</v>
       </c>
       <c r="N3" t="n">
-        <v>413058000</v>
+        <v>321885000</v>
       </c>
       <c r="O3" t="n">
-        <v>413058000</v>
+        <v>321885000</v>
       </c>
       <c r="P3" t="n">
-        <v>-3532000</v>
+        <v>-74373000</v>
       </c>
       <c r="Q3" t="n">
-        <v>145507000</v>
+        <v>145631000</v>
       </c>
       <c r="R3" t="n">
         <v>2575000</v>
@@ -1763,174 +1761,174 @@
         <v>2575000</v>
       </c>
       <c r="T3" t="n">
-        <v>1566846000</v>
+        <v>1727486000</v>
       </c>
       <c r="U3" t="n">
-        <v>1179589000</v>
+        <v>1388736000</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2031000</v>
       </c>
       <c r="W3" t="n">
-        <v>60152000</v>
+        <v>34718000</v>
       </c>
       <c r="X3" t="n">
-        <v>1119437000</v>
+        <v>1351987000</v>
       </c>
       <c r="Y3" t="n">
-        <v>391794000</v>
+        <v>425557000</v>
       </c>
       <c r="Z3" t="n">
-        <v>727643000</v>
+        <v>926430000</v>
       </c>
       <c r="AA3" t="n">
-        <v>387257000</v>
+        <v>338750000</v>
       </c>
       <c r="AB3" t="n">
-        <v>55686000</v>
+        <v>53608000</v>
       </c>
       <c r="AC3" t="n">
-        <v>55686000</v>
+        <v>53608000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2395000</v>
+        <v>2661000</v>
       </c>
       <c r="AE3" t="n">
-        <v>232334000</v>
+        <v>192515000</v>
       </c>
       <c r="AF3" t="n">
-        <v>15321000</v>
+        <v>17267000</v>
       </c>
       <c r="AG3" t="n">
-        <v>75466000</v>
+        <v>67362000</v>
       </c>
       <c r="AH3" t="n">
-        <v>141547000</v>
+        <v>107886000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1979904000</v>
+        <v>2049371000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1820794000</v>
+        <v>1948421000</v>
       </c>
       <c r="AK3" t="n">
-        <v>11944000</v>
+        <v>61367000</v>
       </c>
       <c r="AL3" t="n">
-        <v>18740000</v>
+        <v>23364000</v>
       </c>
       <c r="AM3" t="n">
-        <v>6505000</v>
+        <v>5409000</v>
       </c>
       <c r="AN3" t="n">
-        <v>6505000</v>
+        <v>5409000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1781619000</v>
+        <v>1855542000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1217095000</v>
+        <v>-1275214000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2998714000</v>
+        <v>3130756000</v>
       </c>
       <c r="AR3" t="n">
-        <v>64890000</v>
+        <v>75451000</v>
       </c>
       <c r="AS3" t="n">
-        <v>395353000</v>
+        <v>557262000</v>
       </c>
       <c r="AT3" t="n">
-        <v>763384000</v>
+        <v>731115000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1775087000</v>
+        <v>1766928000</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>159110000</v>
+        <v>100950000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1361000</v>
+        <v>2001000</v>
       </c>
       <c r="AY3" t="n">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21999000</v>
+        <v>7998000</v>
       </c>
       <c r="BA3" t="n">
-        <v>34558000</v>
+        <v>26402000</v>
       </c>
       <c r="BB3" t="n">
-        <v>34558000</v>
+        <v>26402000</v>
       </c>
       <c r="BC3" t="n">
-        <v>5268000</v>
+        <v>21402000</v>
       </c>
       <c r="BD3" t="n">
-        <v>8351000</v>
+        <v>2000000</v>
       </c>
       <c r="BE3" t="n">
-        <v>87173000</v>
+        <v>40347000</v>
       </c>
       <c r="BF3" t="n">
-        <v>87173000</v>
+        <v>40347000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
-        <v>4416005</v>
+        <v>6360365</v>
       </c>
       <c r="C4" t="n">
-        <v>124334150</v>
+        <v>122389790</v>
       </c>
       <c r="D4" t="n">
         <v>128750155</v>
       </c>
       <c r="E4" t="n">
-        <v>886083000</v>
+        <v>640470000</v>
       </c>
       <c r="F4" t="n">
-        <v>1405595000</v>
+        <v>1175123000</v>
       </c>
       <c r="G4" t="n">
-        <v>316476000</v>
+        <v>406553000</v>
       </c>
       <c r="H4" t="n">
-        <v>1248315000</v>
+        <v>1140701000</v>
       </c>
       <c r="I4" t="n">
-        <v>-237800000</v>
+        <v>-228147000</v>
       </c>
       <c r="J4" t="n">
-        <v>316476000</v>
+        <v>406553000</v>
       </c>
       <c r="K4" t="n">
-        <v>479165000</v>
+        <v>447480000</v>
       </c>
       <c r="L4" t="n">
-        <v>321885000</v>
+        <v>413058000</v>
       </c>
       <c r="M4" t="n">
-        <v>1248315000</v>
+        <v>1140701000</v>
       </c>
       <c r="N4" t="n">
-        <v>321885000</v>
+        <v>413058000</v>
       </c>
       <c r="O4" t="n">
-        <v>321885000</v>
+        <v>413058000</v>
       </c>
       <c r="P4" t="n">
-        <v>-74373000</v>
+        <v>-3532000</v>
       </c>
       <c r="Q4" t="n">
-        <v>145631000</v>
+        <v>145507000</v>
       </c>
       <c r="R4" t="n">
         <v>2575000</v>
@@ -1939,295 +1937,297 @@
         <v>2575000</v>
       </c>
       <c r="T4" t="n">
-        <v>1727486000</v>
+        <v>1566846000</v>
       </c>
       <c r="U4" t="n">
-        <v>1388736000</v>
+        <v>1179589000</v>
       </c>
       <c r="V4" t="n">
-        <v>2031000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>34718000</v>
+        <v>60152000</v>
       </c>
       <c r="X4" t="n">
-        <v>1351987000</v>
+        <v>1119437000</v>
       </c>
       <c r="Y4" t="n">
-        <v>425557000</v>
+        <v>391794000</v>
       </c>
       <c r="Z4" t="n">
-        <v>926430000</v>
+        <v>727643000</v>
       </c>
       <c r="AA4" t="n">
-        <v>338750000</v>
+        <v>387257000</v>
       </c>
       <c r="AB4" t="n">
-        <v>53608000</v>
+        <v>55686000</v>
       </c>
       <c r="AC4" t="n">
-        <v>53608000</v>
+        <v>55686000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2661000</v>
+        <v>2395000</v>
       </c>
       <c r="AE4" t="n">
-        <v>192515000</v>
+        <v>232334000</v>
       </c>
       <c r="AF4" t="n">
-        <v>17267000</v>
+        <v>15321000</v>
       </c>
       <c r="AG4" t="n">
-        <v>67362000</v>
+        <v>75466000</v>
       </c>
       <c r="AH4" t="n">
-        <v>107886000</v>
+        <v>141547000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2049371000</v>
+        <v>1979904000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1948421000</v>
+        <v>1820794000</v>
       </c>
       <c r="AK4" t="n">
-        <v>61367000</v>
+        <v>11944000</v>
       </c>
       <c r="AL4" t="n">
-        <v>23364000</v>
+        <v>18740000</v>
       </c>
       <c r="AM4" t="n">
-        <v>5409000</v>
+        <v>6505000</v>
       </c>
       <c r="AN4" t="n">
-        <v>5409000</v>
+        <v>6505000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1855542000</v>
+        <v>1781619000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1275214000</v>
+        <v>-1217095000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3130756000</v>
+        <v>2998714000</v>
       </c>
       <c r="AR4" t="n">
-        <v>75451000</v>
+        <v>64890000</v>
       </c>
       <c r="AS4" t="n">
-        <v>557262000</v>
+        <v>395353000</v>
       </c>
       <c r="AT4" t="n">
-        <v>731115000</v>
+        <v>763384000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1766928000</v>
+        <v>1775087000</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>100950000</v>
+        <v>159110000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2001000</v>
+        <v>1361000</v>
       </c>
       <c r="AY4" t="n">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7998000</v>
+        <v>21999000</v>
       </c>
       <c r="BA4" t="n">
-        <v>26402000</v>
+        <v>34558000</v>
       </c>
       <c r="BB4" t="n">
-        <v>26402000</v>
+        <v>34558000</v>
       </c>
       <c r="BC4" t="n">
-        <v>21402000</v>
+        <v>5268000</v>
       </c>
       <c r="BD4" t="n">
-        <v>2000000</v>
+        <v>8351000</v>
       </c>
       <c r="BE4" t="n">
-        <v>40347000</v>
+        <v>87173000</v>
       </c>
       <c r="BF4" t="n">
-        <v>40347000</v>
+        <v>87173000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45504</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7637465</v>
+      </c>
       <c r="C5" t="n">
-        <v>128750155</v>
+        <v>115984731</v>
       </c>
       <c r="D5" t="n">
-        <v>128750155</v>
+        <v>123622196</v>
       </c>
       <c r="E5" t="n">
-        <v>829231000</v>
+        <v>661901000</v>
       </c>
       <c r="F5" t="n">
-        <v>1414697000</v>
+        <v>1137376000</v>
       </c>
       <c r="G5" t="n">
-        <v>272619000</v>
+        <v>395694000</v>
       </c>
       <c r="H5" t="n">
-        <v>1152616000</v>
+        <v>1120761000</v>
       </c>
       <c r="I5" t="n">
-        <v>-244111000</v>
+        <v>-229251000</v>
       </c>
       <c r="J5" t="n">
-        <v>272619000</v>
+        <v>395694000</v>
       </c>
       <c r="K5" t="n">
-        <v>540058000</v>
+        <v>418242000</v>
       </c>
       <c r="L5" t="n">
-        <v>277977000</v>
+        <v>401627000</v>
       </c>
       <c r="M5" t="n">
-        <v>1152616000</v>
+        <v>1120761000</v>
       </c>
       <c r="N5" t="n">
-        <v>277977000</v>
+        <v>401627000</v>
       </c>
       <c r="O5" t="n">
-        <v>277977000</v>
+        <v>401627000</v>
       </c>
       <c r="P5" t="n">
-        <v>-87207000</v>
+        <v>44571000</v>
       </c>
       <c r="Q5" t="n">
-        <v>145631000</v>
+        <v>145610000</v>
       </c>
       <c r="R5" t="n">
-        <v>2575000</v>
+        <v>2472000</v>
       </c>
       <c r="S5" t="n">
-        <v>2575000</v>
+        <v>2472000</v>
       </c>
       <c r="T5" t="n">
-        <v>1731681000</v>
+        <v>1502743000</v>
       </c>
       <c r="U5" t="n">
-        <v>1396057000</v>
+        <v>1151354000</v>
       </c>
       <c r="V5" t="n">
-        <v>37643000</v>
+        <v>4073000</v>
       </c>
       <c r="W5" t="n">
-        <v>16546000</v>
+        <v>59487000</v>
       </c>
       <c r="X5" t="n">
-        <v>1341868000</v>
+        <v>1087794000</v>
       </c>
       <c r="Y5" t="n">
-        <v>467229000</v>
+        <v>368660000</v>
       </c>
       <c r="Z5" t="n">
-        <v>874639000</v>
+        <v>719134000</v>
       </c>
       <c r="AA5" t="n">
-        <v>335624000</v>
+        <v>351389000</v>
       </c>
       <c r="AB5" t="n">
-        <v>72829000</v>
+        <v>49582000</v>
       </c>
       <c r="AC5" t="n">
-        <v>72829000</v>
+        <v>49582000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3004000</v>
+        <v>3047000</v>
       </c>
       <c r="AE5" t="n">
-        <v>183914000</v>
+        <v>219998000</v>
       </c>
       <c r="AF5" t="n">
-        <v>27759000</v>
+        <v>16019000</v>
       </c>
       <c r="AG5" t="n">
-        <v>44237000</v>
+        <v>66698000</v>
       </c>
       <c r="AH5" t="n">
-        <v>111918000</v>
+        <v>137281000</v>
       </c>
       <c r="AI5" t="n">
-        <v>2009658000</v>
+        <v>1904370000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1918145000</v>
+        <v>1782232000</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>10533000</v>
+        <v>18290000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5358000</v>
+        <v>5933000</v>
       </c>
       <c r="AN5" t="n">
-        <v>5358000</v>
+        <v>5933000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1902254000</v>
+        <v>1756815000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1146188000</v>
+        <v>-1264336000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3048442000</v>
+        <v>3021151000</v>
       </c>
       <c r="AR5" t="n">
-        <v>63868000</v>
+        <v>57555000</v>
       </c>
       <c r="AS5" t="n">
-        <v>558897000</v>
+        <v>373338000</v>
       </c>
       <c r="AT5" t="n">
-        <v>700311000</v>
+        <v>815134000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1725366000</v>
+        <v>1775124000</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>91513000</v>
+        <v>122138000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1638000</v>
+        <v>1358000</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>2488000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12924000</v>
+        <v>17730000</v>
       </c>
       <c r="BA5" t="n">
-        <v>26853000</v>
+        <v>28404000</v>
       </c>
       <c r="BB5" t="n">
-        <v>26853000</v>
+        <v>28404000</v>
       </c>
       <c r="BC5" t="n">
-        <v>3503000</v>
+        <v>8846000</v>
       </c>
       <c r="BD5" t="n">
-        <v>1187000</v>
+        <v>6079000</v>
       </c>
       <c r="BE5" t="n">
-        <v>45408000</v>
+        <v>57233000</v>
       </c>
       <c r="BF5" t="n">
-        <v>45408000</v>
+        <v>57233000</v>
       </c>
     </row>
   </sheetData>
@@ -2453,500 +2453,500 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
+        <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>62296000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-39505000</v>
-      </c>
+        <v>-92983000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>-4000000</v>
+        <v>-195000000</v>
       </c>
       <c r="E2" t="n">
-        <v>778000</v>
+        <v>100033000</v>
       </c>
       <c r="F2" t="n">
-        <v>-12738000</v>
+        <v>83839000</v>
       </c>
       <c r="G2" t="n">
-        <v>-110266000</v>
+        <v>-57681000</v>
       </c>
       <c r="H2" t="n">
-        <v>57233000</v>
+        <v>45408000</v>
       </c>
       <c r="I2" t="n">
-        <v>87173000</v>
+        <v>174451000</v>
       </c>
       <c r="J2" t="n">
-        <v>-29940000</v>
+        <v>-129043000</v>
       </c>
       <c r="K2" t="n">
-        <v>-103865000</v>
+        <v>-36015000</v>
       </c>
       <c r="L2" t="n">
-        <v>-52243000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-39505000</v>
-      </c>
+        <v>83839000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-12738000</v>
+        <v>83839000</v>
       </c>
       <c r="O2" t="n">
-        <v>-3222000</v>
+        <v>-94967000</v>
       </c>
       <c r="P2" t="n">
-        <v>-3222000</v>
+        <v>-94967000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4000000</v>
+        <v>-195000000</v>
       </c>
       <c r="R2" t="n">
-        <v>778000</v>
+        <v>100033000</v>
       </c>
       <c r="S2" t="n">
-        <v>-98637000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>-57726000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-16858000</v>
+      </c>
       <c r="U2" t="n">
-        <v>-6243000</v>
+        <v>-2620000</v>
       </c>
       <c r="V2" t="n">
-        <v>-6243000</v>
+        <v>-2620000</v>
       </c>
       <c r="W2" t="n">
-        <v>-92394000</v>
+        <v>-55106000</v>
       </c>
       <c r="X2" t="n">
-        <v>17872000</v>
+        <v>2575000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-110266000</v>
+        <v>-57681000</v>
       </c>
       <c r="Z2" t="n">
-        <v>172562000</v>
+        <v>-35302000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-9940000</v>
+        <v>7673000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1765000</v>
+        <v>187000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-66953000</v>
+        <v>-68370000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-22211000</v>
+        <v>14575000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-29072000</v>
+        <v>2585000</v>
       </c>
       <c r="AF2" t="n">
-        <v>6154000</v>
+        <v>-3758000</v>
       </c>
       <c r="AG2" t="n">
-        <v>707000</v>
+        <v>15748000</v>
       </c>
       <c r="AH2" t="n">
-        <v>49832000</v>
+        <v>80003000</v>
       </c>
       <c r="AI2" t="n">
-        <v>11021000</v>
+        <v>10267000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11835000</v>
+        <v>-17630000</v>
       </c>
       <c r="AK2" t="n">
-        <v>102382000</v>
+        <v>120920000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1937000</v>
+        <v>3151000</v>
       </c>
       <c r="AM2" t="n">
-        <v>100445000</v>
+        <v>117769000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1294000</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>13459000</v>
+        <v>940000</v>
       </c>
       <c r="AP2" t="n">
-        <v>48785000</v>
+        <v>-177006000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
-        <v>289202000</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
+        <v>-286000</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-200033000</v>
+        <v>-3542000</v>
       </c>
       <c r="E3" t="n">
-        <v>889000</v>
+        <v>50000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-12332000</v>
+        <v>-12808000</v>
       </c>
       <c r="G3" t="n">
-        <v>-73209000</v>
+        <v>-119633000</v>
       </c>
       <c r="H3" t="n">
-        <v>87173000</v>
+        <v>40347000</v>
       </c>
       <c r="I3" t="n">
-        <v>40347000</v>
+        <v>45408000</v>
       </c>
       <c r="J3" t="n">
-        <v>46826000</v>
+        <v>-5061000</v>
       </c>
       <c r="K3" t="n">
-        <v>-248410000</v>
+        <v>-12209000</v>
       </c>
       <c r="L3" t="n">
-        <v>-12332000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
+        <v>-12808000</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>-12332000</v>
+        <v>-12808000</v>
       </c>
       <c r="O3" t="n">
-        <v>-199144000</v>
+        <v>46458000</v>
       </c>
       <c r="P3" t="n">
-        <v>-199144000</v>
+        <v>46458000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-200033000</v>
+        <v>-3542000</v>
       </c>
       <c r="R3" t="n">
-        <v>889000</v>
+        <v>50000000</v>
       </c>
       <c r="S3" t="n">
-        <v>-67175000</v>
+        <v>-112199000</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>-5315000</v>
+        <v>-3113000</v>
       </c>
       <c r="V3" t="n">
-        <v>-5315000</v>
+        <v>-3113000</v>
       </c>
       <c r="W3" t="n">
-        <v>-61860000</v>
+        <v>-109086000</v>
       </c>
       <c r="X3" t="n">
-        <v>11349000</v>
+        <v>10547000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-73209000</v>
+        <v>-119633000</v>
       </c>
       <c r="Z3" t="n">
-        <v>362411000</v>
+        <v>119347000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-12200000</v>
+        <v>-715000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1011000</v>
+        <v>97000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-66499000</v>
+        <v>-58545000</v>
       </c>
       <c r="AD3" t="n">
-        <v>33413000</v>
+        <v>3166000</v>
       </c>
       <c r="AE3" t="n">
-        <v>39437000</v>
+        <v>14885000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-8157000</v>
+        <v>452000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2133000</v>
+        <v>-12171000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-22042000</v>
+        <v>12018000</v>
       </c>
       <c r="AI3" t="n">
-        <v>10545000</v>
+        <v>5874000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30924000</v>
+        <v>7002000</v>
       </c>
       <c r="AK3" t="n">
-        <v>109741000</v>
+        <v>116845000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1827000</v>
+        <v>3240000</v>
       </c>
       <c r="AM3" t="n">
-        <v>107914000</v>
+        <v>113605000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1633000</v>
+        <v>-1474000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8598000</v>
+        <v>-3892000</v>
       </c>
       <c r="AP3" t="n">
-        <v>59587000</v>
+        <v>19267000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
-        <v>-286000</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>289202000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" t="n">
-        <v>-3542000</v>
+        <v>-200033000</v>
       </c>
       <c r="E4" t="n">
-        <v>50000000</v>
+        <v>889000</v>
       </c>
       <c r="F4" t="n">
-        <v>-12808000</v>
+        <v>-12332000</v>
       </c>
       <c r="G4" t="n">
-        <v>-119633000</v>
+        <v>-73209000</v>
       </c>
       <c r="H4" t="n">
+        <v>87173000</v>
+      </c>
+      <c r="I4" t="n">
         <v>40347000</v>
       </c>
-      <c r="I4" t="n">
-        <v>45408000</v>
-      </c>
       <c r="J4" t="n">
-        <v>-5061000</v>
+        <v>46826000</v>
       </c>
       <c r="K4" t="n">
-        <v>-12209000</v>
+        <v>-248410000</v>
       </c>
       <c r="L4" t="n">
-        <v>-12808000</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>-12332000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>-12808000</v>
+        <v>-12332000</v>
       </c>
       <c r="O4" t="n">
-        <v>46458000</v>
+        <v>-199144000</v>
       </c>
       <c r="P4" t="n">
-        <v>46458000</v>
+        <v>-199144000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3542000</v>
+        <v>-200033000</v>
       </c>
       <c r="R4" t="n">
-        <v>50000000</v>
+        <v>889000</v>
       </c>
       <c r="S4" t="n">
-        <v>-112199000</v>
+        <v>-67175000</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-3113000</v>
+        <v>-5315000</v>
       </c>
       <c r="V4" t="n">
-        <v>-3113000</v>
+        <v>-5315000</v>
       </c>
       <c r="W4" t="n">
-        <v>-109086000</v>
+        <v>-61860000</v>
       </c>
       <c r="X4" t="n">
-        <v>10547000</v>
+        <v>11349000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-119633000</v>
+        <v>-73209000</v>
       </c>
       <c r="Z4" t="n">
-        <v>119347000</v>
+        <v>362411000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-715000</v>
+        <v>-12200000</v>
       </c>
       <c r="AB4" t="n">
-        <v>97000</v>
+        <v>1011000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-58545000</v>
+        <v>-66499000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3166000</v>
+        <v>33413000</v>
       </c>
       <c r="AE4" t="n">
-        <v>14885000</v>
+        <v>39437000</v>
       </c>
       <c r="AF4" t="n">
-        <v>452000</v>
+        <v>-8157000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-12171000</v>
+        <v>2133000</v>
       </c>
       <c r="AH4" t="n">
-        <v>12018000</v>
+        <v>-22042000</v>
       </c>
       <c r="AI4" t="n">
-        <v>5874000</v>
+        <v>10545000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7002000</v>
+        <v>30924000</v>
       </c>
       <c r="AK4" t="n">
-        <v>116845000</v>
+        <v>109741000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3240000</v>
+        <v>1827000</v>
       </c>
       <c r="AM4" t="n">
-        <v>113605000</v>
+        <v>107914000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1474000</v>
+        <v>1633000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-3892000</v>
+        <v>8598000</v>
       </c>
       <c r="AP4" t="n">
-        <v>19267000</v>
+        <v>59587000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
+        <v>45504</v>
       </c>
       <c r="B5" t="n">
-        <v>-92983000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>62296000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-39505000</v>
+      </c>
       <c r="D5" t="n">
-        <v>-195000000</v>
+        <v>-4000000</v>
       </c>
       <c r="E5" t="n">
-        <v>100033000</v>
+        <v>778000</v>
       </c>
       <c r="F5" t="n">
-        <v>83839000</v>
+        <v>-12738000</v>
       </c>
       <c r="G5" t="n">
-        <v>-57681000</v>
+        <v>-110266000</v>
       </c>
       <c r="H5" t="n">
-        <v>45408000</v>
+        <v>57233000</v>
       </c>
       <c r="I5" t="n">
-        <v>174451000</v>
+        <v>87173000</v>
       </c>
       <c r="J5" t="n">
-        <v>-129043000</v>
+        <v>-29940000</v>
       </c>
       <c r="K5" t="n">
-        <v>-36015000</v>
+        <v>-103865000</v>
       </c>
       <c r="L5" t="n">
-        <v>83839000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-52243000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-39505000</v>
+      </c>
       <c r="N5" t="n">
-        <v>83839000</v>
+        <v>-12738000</v>
       </c>
       <c r="O5" t="n">
-        <v>-94967000</v>
+        <v>-3222000</v>
       </c>
       <c r="P5" t="n">
-        <v>-94967000</v>
+        <v>-3222000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-195000000</v>
+        <v>-4000000</v>
       </c>
       <c r="R5" t="n">
-        <v>100033000</v>
+        <v>778000</v>
       </c>
       <c r="S5" t="n">
-        <v>-57726000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-16858000</v>
-      </c>
+        <v>-98637000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-2620000</v>
+        <v>-6243000</v>
       </c>
       <c r="V5" t="n">
-        <v>-2620000</v>
+        <v>-6243000</v>
       </c>
       <c r="W5" t="n">
-        <v>-55106000</v>
+        <v>-92394000</v>
       </c>
       <c r="X5" t="n">
-        <v>2575000</v>
+        <v>17872000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-57681000</v>
+        <v>-110266000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-35302000</v>
+        <v>172562000</v>
       </c>
       <c r="AA5" t="n">
-        <v>7673000</v>
+        <v>-9940000</v>
       </c>
       <c r="AB5" t="n">
-        <v>187000</v>
+        <v>1765000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-68370000</v>
+        <v>-66953000</v>
       </c>
       <c r="AD5" t="n">
-        <v>14575000</v>
+        <v>-22211000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2585000</v>
+        <v>-29072000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-3758000</v>
+        <v>6154000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15748000</v>
+        <v>707000</v>
       </c>
       <c r="AH5" t="n">
-        <v>80003000</v>
+        <v>49832000</v>
       </c>
       <c r="AI5" t="n">
-        <v>10267000</v>
+        <v>11021000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-17630000</v>
+        <v>11835000</v>
       </c>
       <c r="AK5" t="n">
-        <v>120920000</v>
+        <v>102382000</v>
       </c>
       <c r="AL5" t="n">
-        <v>3151000</v>
+        <v>1937000</v>
       </c>
       <c r="AM5" t="n">
-        <v>117769000</v>
+        <v>100445000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-1294000</v>
       </c>
       <c r="AO5" t="n">
-        <v>940000</v>
+        <v>13459000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-177006000</v>
+        <v>48785000</v>
       </c>
     </row>
   </sheetData>
@@ -2960,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EV2"/>
+  <dimension ref="A1:EU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3546,180 +3546,175 @@
       </c>
       <c r="DM1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
       <c r="EU1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3801,7 +3796,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Timothy Randall Martin', 'age': 70, 'title': 'Executive Chairman', 'yearBorn': 1955, 'fiscalYear': 2025, 'totalPay': 391448, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Hutson', 'age': 60, 'title': 'CEO, Member of Management Board &amp; Executive Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 993053, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ben  Whitley', 'age': 47, 'title': 'Finance Director, Member of Management Board &amp; Executive Director', 'yearBorn': 1978, 'fiscalYear': 2025, 'totalPay': 415697, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James  Ullman', 'age': 54, 'title': 'Personnel &amp; Retail Audit Director, Member of Management Board and Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 338331, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Martin  Geoghegan', 'age': 56, 'title': 'Operations Director &amp; Member of Management Board', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 394912, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David  Capstick', 'age': 64, 'title': 'IT &amp; Property Director and Member of Management Board', 'yearBorn': 1961, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nigel  Connor', 'age': 56, 'title': 'Company Secretary, Legal Director, Member of Management Board &amp; Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michael  Barron', 'age': 39, 'title': 'Commercial Director &amp; Member of Management Board', 'yearBorn': 1986, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Paul  Brimmer', 'age': 50, 'title': 'Purchasing Director &amp; Member of Management Board', 'yearBorn': 1975, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tom  Ball', 'age': 49, 'title': 'People Director &amp; Member of Management Board', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Timothy Randall Martin', 'age': 70, 'title': 'Executive Chairman', 'yearBorn': 1955, 'fiscalYear': 2025, 'totalPay': 390588, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Hutson', 'age': 60, 'title': 'CEO, Member of Management Board &amp; Executive Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 990871, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ben  Whitley', 'age': 47, 'title': 'Finance Director, Member of Management Board &amp; Executive Director', 'yearBorn': 1978, 'fiscalYear': 2025, 'totalPay': 414783, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James  Ullman', 'age': 54, 'title': 'Personnel &amp; Retail Audit Director, Member of Management Board and Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 337588, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Martin  Geoghegan', 'age': 56, 'title': 'Operations Director &amp; Member of Management Board', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 394044, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David  Capstick', 'age': 64, 'title': 'IT &amp; Property Director and Member of Management Board', 'yearBorn': 1961, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nigel  Connor', 'age': 56, 'title': 'Company Secretary, Legal Director, Member of Management Board &amp; Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michael  Barron', 'age': 39, 'title': 'Commercial Director &amp; Member of Management Board', 'yearBorn': 1986, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Paul  Brimmer', 'age': 50, 'title': 'Purchasing Director &amp; Member of Management Board', 'yearBorn': 1975, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tom  Ball', 'age': 49, 'title': 'People Director &amp; Member of Management Board', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3820,7 +3815,7 @@
         <v>9</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1767139200</v>
@@ -3837,34 +3832,34 @@
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.05</v>
+        <v>7.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.05</v>
+        <v>7.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>7.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>7.05</v>
+        <v>7.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.05</v>
+        <v>7.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="AI2" t="n">
         <v>0.14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AK2" t="n">
         <v>1778112000</v>
@@ -3873,31 +3868,31 @@
         <v>0.28170002</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.108</v>
+        <v>1.126</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.681818</v>
+        <v>11.23077</v>
       </c>
       <c r="AO2" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AP2" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AQ2" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.45</v>
+        <v>7.7</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3906,10 +3901,10 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>743109824</v>
+        <v>769461248</v>
       </c>
       <c r="AY2" t="n">
-        <v>754621937</v>
+        <v>796658932</v>
       </c>
       <c r="AZ2" t="n">
         <v>6.2</v>
@@ -3924,19 +3919,19 @@
         <v>4.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.33997187</v>
+        <v>0.35202762</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.829</v>
+        <v>7.021</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.522</v>
+        <v>7.48775</v>
       </c>
       <c r="BG2" t="n">
         <v>0.12</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.017021276</v>
+        <v>0.014906832</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
@@ -3947,31 +3942,31 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>1920899968</v>
+        <v>1946883328</v>
       </c>
       <c r="BL2" t="n">
         <v>0.02523</v>
       </c>
       <c r="BM2" t="n">
-        <v>61228247</v>
+        <v>60785491</v>
       </c>
       <c r="BN2" t="n">
         <v>105405650</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.42123002</v>
+        <v>0.42366</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.48956</v>
+        <v>0.47047</v>
       </c>
       <c r="BQ2" t="n">
         <v>105405650</v>
       </c>
       <c r="BR2" t="n">
-        <v>3.7274144</v>
+        <v>3.7192235</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.8913916</v>
+        <v>1.9627753</v>
       </c>
       <c r="BT2" t="n">
         <v>1753574400</v>
@@ -3989,19 +3984,19 @@
         <v>55150000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.879</v>
+        <v>0.891</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.321999999999999</v>
+        <v>9.448</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0.18965518</v>
+        <v>-0.052941203</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CD2" t="n">
         <v>0.04</v>
@@ -4015,7 +4010,7 @@
         </is>
       </c>
       <c r="CG2" t="n">
-        <v>7.05</v>
+        <v>7.3</v>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
@@ -4118,144 +4113,141 @@
         </is>
       </c>
       <c r="DJ2" t="n">
+        <v>-9.31677</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Wetherspoon (J D)             R</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>7.3 - 7.3</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1.1000004</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.17741942</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>6.2 - 9.15</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-1.8499994</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.20218574</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-5.2941203</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1774040400</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1774040400</v>
+      </c>
+      <c r="DZ2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
+      <c r="EA2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.27900028</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.03973797</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.18774986</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.02507427</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1540274400000</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EL2" t="n">
+        <v>1782134701</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>finmb_881715</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="ES2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET2" t="inlineStr">
         <is>
           <t>J D Wetherspoon plc</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>1780406701</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>finmb_881715</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1540274400000</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>7.05 - 7.1</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>39</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.8500004</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.13709684</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>6.2 - 9.15</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-2.0999994</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.22950815</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-18.965519</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1774040400</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1774040400</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1774040400</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.2210002</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.032362014</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-0.47199965</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.06274921999999999</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ET2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>Wetherspoon (J D)             R</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
